--- a/e2.xlsx
+++ b/e2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\excel-compare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A8C1C0-C56C-446F-A550-F166EB4F6C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA2D1DC-04A8-4A1C-841F-B87274225F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="11415" windowHeight="13433" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>系统名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,15 +170,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BBC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>DC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50000012345003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50000012345001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50000012345001.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50000012345002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -222,8 +238,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -664,6 +681,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB58F60-3710-4747-A0DB-B80F002340AE}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="35.9296875" customWidth="1"/>
+    <col min="4" max="4" width="15.3984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -681,44 +702,44 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="C2">
-        <v>11100</v>
-      </c>
-      <c r="D2">
-        <v>91</v>
+      <c r="C2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="C3">
-        <v>98999.1</v>
-      </c>
-      <c r="D3">
-        <v>121</v>
+      <c r="C3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
       </c>
-      <c r="C4">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D4">
-        <v>1.1000000000000001</v>
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
